--- a/DRIVE/1. Direção/2. Financeiro/2.2 Contabilidade/Compras/Proposta SR - PA JBL/Divisão de compra.xlsx
+++ b/DRIVE/1. Direção/2. Financeiro/2.2 Contabilidade/Compras/Proposta SR - PA JBL/Divisão de compra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruisa\mind7\MINDSET\DRIVE\1. Direção\2. Financeiro\2.2 Contabilidade\Compras\Proposta SR - PA JBL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8FE356-A81E-4012-86A8-537F0CE63A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35573709-BBBD-4F53-8ECA-37117A9DF79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9FEF305E-DE7E-4357-B4A2-9AE6791F5EA4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Rui Alves</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Mateus</t>
-  </si>
-  <si>
-    <t>Acessórios</t>
   </si>
   <si>
     <t>Investimento</t>
@@ -453,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039C83DE-24BC-430E-B8A4-170A66031777}">
-  <dimension ref="G6:L14"/>
+  <dimension ref="G7:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
@@ -462,26 +459,18 @@
     <col min="12" max="12" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="K6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1450</v>
-      </c>
-    </row>
     <row r="7" spans="7:12" x14ac:dyDescent="0.3">
       <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
         <v>10</v>
       </c>
-      <c r="I7" t="s">
-        <v>11</v>
-      </c>
       <c r="K7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L7" s="1">
-        <v>300</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="8" spans="7:12" x14ac:dyDescent="0.3">
@@ -500,7 +489,7 @@
       </c>
       <c r="L8">
         <f>SUM(H8:H16)</f>
-        <v>1500</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="9" spans="7:12" x14ac:dyDescent="0.3">
@@ -515,11 +504,11 @@
         <v>300</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L9">
         <f>SUM(I8:I14)</f>
-        <v>2250</v>
+        <v>2377.5</v>
       </c>
     </row>
     <row r="10" spans="7:12" x14ac:dyDescent="0.3">
@@ -551,15 +540,15 @@
         <v>4</v>
       </c>
       <c r="H12">
-        <v>300</v>
+        <v>385</v>
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>577.5</v>
       </c>
       <c r="L12">
         <f>L9/6</f>
-        <v>375</v>
+        <v>396.25</v>
       </c>
     </row>
     <row r="13" spans="7:12" x14ac:dyDescent="0.3">
